--- a/examples/external-apis/petstore/review/cases.xlsx
+++ b/examples/external-apis/petstore/review/cases.xlsx
@@ -504,7 +504,7 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Track</t>
+          <t>Suite</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
@@ -1060,7 +1060,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>2. You may change Title, Criteria, Priority, Track and Tags. Steps are changed in the case file.</t>
+          <t>2. You may change Title, Criteria, Priority, Suite and Tags. Steps are changed in the case file.</t>
         </is>
       </c>
     </row>

--- a/examples/external-apis/petstore/review/cases.xlsx
+++ b/examples/external-apis/petstore/review/cases.xlsx
@@ -1081,7 +1081,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>5. Save, then run: qa-agent review import</t>
+          <t>5. Save, then run: qa-agent review apply</t>
         </is>
       </c>
     </row>
